--- a/artfynd/A 33653-2025 artfynd.xlsx
+++ b/artfynd/A 33653-2025 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning</t>
+          <t>Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 33653-2025 artfynd.xlsx
+++ b/artfynd/A 33653-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131020449</v>
       </c>
       <c r="B2" t="n">
-        <v>98931</v>
+        <v>98932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 33653-2025 artfynd.xlsx
+++ b/artfynd/A 33653-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131020449</v>
       </c>
       <c r="B2" t="n">
-        <v>98932</v>
+        <v>98935</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33653-2025 artfynd.xlsx
+++ b/artfynd/A 33653-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131020449</v>
       </c>
       <c r="B2" t="n">
-        <v>98935</v>
+        <v>98936</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33653-2025 artfynd.xlsx
+++ b/artfynd/A 33653-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131020449</v>
       </c>
       <c r="B2" t="n">
-        <v>98936</v>
+        <v>98938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33653-2025 artfynd.xlsx
+++ b/artfynd/A 33653-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131020449</v>
       </c>
       <c r="B2" t="n">
-        <v>98938</v>
+        <v>98939</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
